--- a/dashboard/data_pred.xlsx
+++ b/dashboard/data_pred.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\forecasting\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3d9ca122eaf7d8bd/Documents/GitHub/swaper/dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD31089-26B7-4772-8C76-D4E1FB2E3CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{3AD31089-26B7-4772-8C76-D4E1FB2E3CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34F9EF85-E417-4C3C-BD4B-54DEAB787BDC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3B4F240-1C7B-4534-B2F2-ADBAE75C1F39}"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
     <t>Pred_LSTM</t>
   </si>
   <si>
-    <t>Pred_RF</t>
+    <t>Pred_SARIMA</t>
   </si>
 </sst>
 </file>
@@ -130,6 +130,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -482,7 +486,7 @@
         <v>1206</v>
       </c>
       <c r="D2">
-        <v>1421</v>
+        <v>1013</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -497,7 +501,7 @@
         <v>1010</v>
       </c>
       <c r="D3">
-        <v>1413</v>
+        <v>923</v>
       </c>
       <c r="E3" s="3"/>
     </row>
@@ -512,7 +516,7 @@
         <v>926</v>
       </c>
       <c r="D4">
-        <v>1398</v>
+        <v>821</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -527,7 +531,7 @@
         <v>626</v>
       </c>
       <c r="D5">
-        <v>1396</v>
+        <v>620</v>
       </c>
       <c r="E5" s="3"/>
     </row>
@@ -542,7 +546,7 @@
         <v>993</v>
       </c>
       <c r="D6">
-        <v>1387</v>
+        <v>610</v>
       </c>
       <c r="E6" s="3"/>
     </row>
@@ -557,7 +561,7 @@
         <v>935</v>
       </c>
       <c r="D7">
-        <v>1447</v>
+        <v>648</v>
       </c>
       <c r="E7" s="3"/>
     </row>
@@ -572,7 +576,7 @@
         <v>815</v>
       </c>
       <c r="D8">
-        <v>1501</v>
+        <v>637</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -587,7 +591,7 @@
         <v>714</v>
       </c>
       <c r="D9">
-        <v>1623</v>
+        <v>509</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -602,7 +606,7 @@
         <v>669</v>
       </c>
       <c r="D10">
-        <v>1637</v>
+        <v>490</v>
       </c>
       <c r="E10" s="3"/>
     </row>
@@ -617,7 +621,7 @@
         <v>797</v>
       </c>
       <c r="D11">
-        <v>1622</v>
+        <v>557</v>
       </c>
       <c r="E11" s="3"/>
     </row>
@@ -632,7 +636,7 @@
         <v>772</v>
       </c>
       <c r="D12">
-        <v>1631</v>
+        <v>517</v>
       </c>
       <c r="E12" s="3"/>
     </row>
@@ -647,7 +651,7 @@
         <v>707</v>
       </c>
       <c r="D13">
-        <v>1521</v>
+        <v>494</v>
       </c>
       <c r="E13" s="3"/>
     </row>

--- a/dashboard/data_pred.xlsx
+++ b/dashboard/data_pred.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3d9ca122eaf7d8bd/Documents/GitHub/swaper/dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\swaper\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{3AD31089-26B7-4772-8C76-D4E1FB2E3CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34F9EF85-E417-4C3C-BD4B-54DEAB787BDC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63494546-645D-40B2-8710-5E72ADE3616C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3B4F240-1C7B-4534-B2F2-ADBAE75C1F39}"/>
   </bookViews>
@@ -130,10 +130,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -665,6 +661,9 @@
       <c r="C14" s="1">
         <v>609</v>
       </c>
+      <c r="D14">
+        <v>440</v>
+      </c>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -677,6 +676,9 @@
       <c r="C15" s="1">
         <v>529</v>
       </c>
+      <c r="D15">
+        <v>417</v>
+      </c>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -689,6 +691,9 @@
       <c r="C16" s="1">
         <v>599</v>
       </c>
+      <c r="D16">
+        <v>425</v>
+      </c>
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -701,6 +706,9 @@
       <c r="C17" s="1">
         <v>569</v>
       </c>
+      <c r="D17">
+        <v>420</v>
+      </c>
       <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -713,6 +721,9 @@
       <c r="C18" s="1">
         <v>408</v>
       </c>
+      <c r="D18">
+        <v>456</v>
+      </c>
       <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -725,6 +736,9 @@
       <c r="C19" s="1">
         <v>567</v>
       </c>
+      <c r="D19">
+        <v>319</v>
+      </c>
       <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -737,6 +751,9 @@
       <c r="C20" s="1">
         <v>573</v>
       </c>
+      <c r="D20">
+        <v>446</v>
+      </c>
       <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -749,6 +766,9 @@
       <c r="C21" s="1">
         <v>565</v>
       </c>
+      <c r="D21">
+        <v>476</v>
+      </c>
       <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -761,6 +781,9 @@
       <c r="C22" s="1">
         <v>525</v>
       </c>
+      <c r="D22">
+        <v>460</v>
+      </c>
       <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -773,6 +796,9 @@
       <c r="C23" s="1">
         <v>688</v>
       </c>
+      <c r="D23">
+        <v>459</v>
+      </c>
       <c r="E23" s="3"/>
     </row>
     <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -785,6 +811,9 @@
       <c r="C24" s="1">
         <v>864</v>
       </c>
+      <c r="D24">
+        <v>544</v>
+      </c>
       <c r="E24" s="3"/>
     </row>
     <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -796,6 +825,9 @@
       </c>
       <c r="C25" s="1">
         <v>1071</v>
+      </c>
+      <c r="D25">
+        <v>524</v>
       </c>
       <c r="E25" s="3"/>
     </row>

--- a/dashboard/data_pred.xlsx
+++ b/dashboard/data_pred.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\swaper\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63494546-645D-40B2-8710-5E72ADE3616C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5EB2AF-5EB6-4864-AE11-6096CFA5328D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3B4F240-1C7B-4534-B2F2-ADBAE75C1F39}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>Pred_SARIMA</t>
+  </si>
+  <si>
+    <t>Pred_RF</t>
   </si>
 </sst>
 </file>
@@ -469,7 +472,9 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -651,7 +656,7 @@
       </c>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2026</v>
       </c>
@@ -664,9 +669,11 @@
       <c r="D14">
         <v>440</v>
       </c>
-      <c r="E14" s="3"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2026</v>
       </c>
@@ -679,9 +686,11 @@
       <c r="D15">
         <v>417</v>
       </c>
-      <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2026</v>
       </c>
@@ -694,9 +703,11 @@
       <c r="D16">
         <v>425</v>
       </c>
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="E16">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2026</v>
       </c>
@@ -709,9 +720,11 @@
       <c r="D17">
         <v>420</v>
       </c>
-      <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -724,9 +737,11 @@
       <c r="D18">
         <v>456</v>
       </c>
-      <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>2026</v>
       </c>
@@ -739,9 +754,11 @@
       <c r="D19">
         <v>319</v>
       </c>
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2026</v>
       </c>
@@ -754,9 +771,11 @@
       <c r="D20">
         <v>446</v>
       </c>
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>2026</v>
       </c>
@@ -769,9 +788,11 @@
       <c r="D21">
         <v>476</v>
       </c>
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="E21">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>2026</v>
       </c>
@@ -784,9 +805,11 @@
       <c r="D22">
         <v>460</v>
       </c>
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2026</v>
       </c>
@@ -799,9 +822,11 @@
       <c r="D23">
         <v>459</v>
       </c>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2026</v>
       </c>
@@ -814,9 +839,11 @@
       <c r="D24">
         <v>544</v>
       </c>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="E24">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2026</v>
       </c>
@@ -829,7 +856,9 @@
       <c r="D25">
         <v>524</v>
       </c>
-      <c r="E25" s="3"/>
+      <c r="E25">
+        <v>545</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
